--- a/Finalisation-concertation/ig/StructureDefinition-FrSimpleQuantityMedication.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-FrSimpleQuantityMedication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:36:59+00:00</t>
+    <t>2026-05-21T12:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Finalisation-concertation/ig/StructureDefinition-FrSimpleQuantityMedication.xlsx
+++ b/Finalisation-concertation/ig/StructureDefinition-FrSimpleQuantityMedication.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/StructureDefinition/FrSimpleQuantityMedication</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/FrSimpleQuantityMedication</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:38:31+00:00</t>
+    <t>2026-05-21T13:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
